--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:14:26+00:00</t>
+    <t>2026-10-14T13:25:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -278,10 +278,10 @@
 </t>
   </si>
   <si>
-    <t>Additional administrative gender (Geschlecht, Ergänzung zu 'other')</t>
-  </si>
-  <si>
-    <t>Additional administrative gender code (Geschlecht) required in Austria that is not covered by the FHIR administrative gender codes. The extension is only applied in case the administrative gender itself is set to 'other'.</t>
+    <t>Additional administrative gender (Geschlecht)</t>
+  </si>
+  <si>
+    <t>Additional administrative gender code (Geschlecht) required in Austria that is not covered by the FHIR administrative gender codes. The extension is only applied in case the administrative gender itself is set to 'other' (Ergänzung zu 'other').</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:25:21+00:00</t>
+    <t>2026-10-19T13:57:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:57:06+00:00</t>
+    <t>2026-10-19T15:00:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:00:46+00:00</t>
+    <t>2026-10-20T05:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
